--- a/analysis/recap/generative.xlsx
+++ b/analysis/recap/generative.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,7 +536,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -563,49 +563,49 @@
         <v>14298463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.822136812949973</v>
+        <v>0.7591704903485398</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.024314536989136</v>
+        <v>1.072426280393171</v>
       </c>
       <c r="K2" t="n">
         <v>1933</v>
       </c>
       <c r="L2" t="n">
-        <v>1980</v>
+        <v>2073</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8898989898989899</v>
+        <v>0.8273034249879402</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8396987627756859</v>
+        <v>0.7771516393442623</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7991944764096662</v>
+        <v>0.736209721463681</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7649969078540507</v>
+        <v>0.7017543859649122</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9211643792590349</v>
+        <v>0.907520706255565</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9214545940436418</v>
+        <v>0.9204136482327201</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8709097569974942</v>
+        <v>0.8693555397395911</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9095532578248179</v>
+        <v>0.9131943700816432</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9087366130663269</v>
+        <v>0.9139601529619304</v>
       </c>
       <c r="V2" t="n">
-        <v>0.167973124300112</v>
+        <v>0.267574931880109</v>
       </c>
     </row>
     <row r="3">
@@ -616,7 +616,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,49 +643,49 @@
         <v>30288239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8486803028341293</v>
+        <v>0.832314689203993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9743268150359059</v>
+        <v>0.9984468033153372</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9746508018623901</v>
+        <v>0.9984480082772892</v>
       </c>
       <c r="K3" t="n">
         <v>1933</v>
       </c>
       <c r="L3" t="n">
-        <v>1884</v>
+        <v>1930</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9283439490445859</v>
+        <v>0.9031088082901555</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8854225751559841</v>
+        <v>0.8524046434494196</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8507917174177831</v>
+        <v>0.8110189573459715</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8231426692965155</v>
+        <v>0.7734524569240587</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9263730893142754</v>
+        <v>0.9176085465582787</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9340303088064077</v>
+        <v>0.919799823457115</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8898243130555756</v>
+        <v>0.8684174198478557</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9291626911631987</v>
+        <v>0.9054591345391456</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9294964985991072</v>
+        <v>0.9066961452662256</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1304591265397536</v>
+        <v>0.1656675749318801</v>
       </c>
     </row>
     <row r="4">
@@ -696,7 +696,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -723,49 +723,49 @@
         <v>42511865</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8274140100749369</v>
+        <v>0.8371441568751745</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.028453181583032</v>
+        <v>1.000517330574237</v>
       </c>
       <c r="K4" t="n">
         <v>1933</v>
       </c>
       <c r="L4" t="n">
-        <v>1988</v>
+        <v>1934</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8983903420523138</v>
+        <v>0.9043433298862461</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8468130690948045</v>
+        <v>0.8560397131825703</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8041237113402062</v>
+        <v>0.8156028368794326</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7661538461538462</v>
+        <v>0.7778485041374921</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9263308288857423</v>
+        <v>0.9232654012374517</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9268839311756601</v>
+        <v>0.9265694155726554</v>
       </c>
       <c r="S4" t="n">
-        <v>0.871446438049909</v>
+        <v>0.8809775532910336</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9102409738786095</v>
+        <v>0.9130816944441722</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9100588148965953</v>
+        <v>0.9130838037254323</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1567749160134378</v>
+        <v>0.1629427792915531</v>
       </c>
     </row>
     <row r="5">
@@ -776,7 +776,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -803,49 +803,49 @@
         <v>50995999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8332073444285105</v>
+        <v>0.8378876874925361</v>
       </c>
       <c r="I5" t="n">
-        <v>0.982781540518583</v>
+        <v>0.9759174085910376</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9829280910501811</v>
+        <v>0.9762027935851009</v>
       </c>
       <c r="K5" t="n">
         <v>1933</v>
       </c>
       <c r="L5" t="n">
-        <v>1900</v>
+        <v>1887</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9194736842105263</v>
+        <v>0.9226285108638049</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8662169758291175</v>
+        <v>0.8759909399773499</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8232810615199035</v>
+        <v>0.8370820668693009</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7878985035783995</v>
+        <v>0.8031496062992126</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9236102311247406</v>
+        <v>0.9232756619765364</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9310793921482011</v>
+        <v>0.9286084589591487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.883308390137953</v>
+        <v>0.880719507968899</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9235135532843646</v>
+        <v>0.9215673439450756</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9224608022664224</v>
+        <v>0.9202389218805785</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1399776035834266</v>
+        <v>0.1411444141689373</v>
       </c>
     </row>
     <row r="6">
@@ -856,7 +856,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -883,49 +883,49 @@
         <v>246773155</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8289309166714438</v>
+        <v>0.8228977384270612</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9732650479830102</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9736161407139162</v>
+        <v>1.016037247801345</v>
       </c>
       <c r="K6" t="n">
         <v>1933</v>
       </c>
       <c r="L6" t="n">
-        <v>1882</v>
+        <v>1964</v>
       </c>
       <c r="M6" t="n">
-        <v>0.926673751328374</v>
+        <v>0.8910386965376782</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8705281090289608</v>
+        <v>0.8404774823657081</v>
       </c>
       <c r="O6" t="n">
-        <v>0.825</v>
+        <v>0.8002322880371661</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7906517445687953</v>
+        <v>0.7651467832604623</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9129486349582845</v>
+        <v>0.9137721012614559</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9239776276012144</v>
+        <v>0.9153677059217793</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8598906281025464</v>
+        <v>0.8616344457025578</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9079476089854517</v>
+        <v>0.8996736027314399</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9080376456215742</v>
+        <v>0.8997840996536988</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1478163493840985</v>
+        <v>0.1803814713896458</v>
       </c>
     </row>
     <row r="7">
@@ -936,7 +936,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -946,66 +946,66 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>14298463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.822136812949973</v>
+        <v>0.6725870561952849</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1.024314536989136</v>
+        <v>1.19762027935851</v>
       </c>
       <c r="K7" t="n">
         <v>1933</v>
       </c>
       <c r="L7" t="n">
-        <v>1980</v>
+        <v>2315</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8898989898989899</v>
+        <v>0.7377969762419007</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8396987627756859</v>
+        <v>0.6905195989061076</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7991944764096662</v>
+        <v>0.6512301013024602</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7649969078540507</v>
+        <v>0.6168032786885246</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9211643792590349</v>
+        <v>0.8949006370867536</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9214545940436418</v>
+        <v>0.9075486100963197</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8709097569974942</v>
+        <v>0.8561231556236251</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9095532578248179</v>
+        <v>0.9030775579493473</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9087366130663269</v>
+        <v>0.9027607608425996</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2087193460490463</v>
+        <v>0.4049046321525885</v>
       </c>
     </row>
     <row r="8">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1026,66 +1026,66 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>30288239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8486803028341293</v>
+        <v>0.7433738395524411</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9743268150359059</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9746508018623901</v>
+        <v>1.10812209001552</v>
       </c>
       <c r="K8" t="n">
         <v>1933</v>
       </c>
       <c r="L8" t="n">
-        <v>1884</v>
+        <v>2142</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9283439490445859</v>
+        <v>0.8127917833800187</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8854225751559841</v>
+        <v>0.7634834240475012</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8507917174177831</v>
+        <v>0.7205263157894737</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8231426692965155</v>
+        <v>0.6829679595278246</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9263730893142754</v>
+        <v>0.9107398285373828</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9340303088064077</v>
+        <v>0.9152850508011117</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8898243130555756</v>
+        <v>0.8613820013723741</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9291626911631987</v>
+        <v>0.8959915410566994</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9294964985991072</v>
+        <v>0.8980888499868982</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1716621253405995</v>
+        <v>0.2931880108991826</v>
       </c>
     </row>
     <row r="9">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1106,66 +1106,66 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>42511865</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8274140100749369</v>
+        <v>0.8298784082270558</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0.9942931413435602</v>
       </c>
       <c r="J9" t="n">
-        <v>1.028453181583032</v>
+        <v>0.9943093636833937</v>
       </c>
       <c r="K9" t="n">
         <v>1933</v>
       </c>
       <c r="L9" t="n">
-        <v>1988</v>
+        <v>1922</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8983903420523138</v>
+        <v>0.904786680541103</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8468130690948045</v>
+        <v>0.8545252637423654</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8041237113402062</v>
+        <v>0.8107142857142857</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7661538461538462</v>
+        <v>0.7742142398973701</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9263308288857423</v>
+        <v>0.912407404489731</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9268839311756601</v>
+        <v>0.9169209782628838</v>
       </c>
       <c r="S9" t="n">
-        <v>0.871446438049909</v>
+        <v>0.8640882817024692</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9102409738786095</v>
+        <v>0.9011551510771202</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9100588148965953</v>
+        <v>0.9012445505467606</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1994550408719346</v>
+        <v>0.1722070844686648</v>
       </c>
     </row>
     <row r="10">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1186,66 +1186,66 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>50995999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8332073444285105</v>
+        <v>0.7708541904666956</v>
       </c>
       <c r="I10" t="n">
-        <v>0.982781540518583</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9829280910501811</v>
+        <v>1.079668908432488</v>
       </c>
       <c r="K10" t="n">
         <v>1933</v>
       </c>
       <c r="L10" t="n">
-        <v>1900</v>
+        <v>2087</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9194736842105263</v>
+        <v>0.836607570675611</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8662169758291175</v>
+        <v>0.7878942014242116</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8232810615199035</v>
+        <v>0.7495934959349594</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7878985035783995</v>
+        <v>0.7146171693735499</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9236102311247406</v>
+        <v>0.9135346028966179</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9310793921482011</v>
+        <v>0.9176873353296402</v>
       </c>
       <c r="S10" t="n">
-        <v>0.883308390137953</v>
+        <v>0.8706757094546296</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9235135532843646</v>
+        <v>0.9016871638358204</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9224608022664224</v>
+        <v>0.9011357846112719</v>
       </c>
       <c r="V10" t="n">
-        <v>0.182016348773842</v>
+        <v>0.2523160762942779</v>
       </c>
     </row>
     <row r="11">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1266,66 +1266,66 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>246773155</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8289309166714438</v>
+        <v>0.8135060789007368</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9732650479830102</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9736161407139162</v>
+        <v>1.025866528711847</v>
       </c>
       <c r="K11" t="n">
         <v>1933</v>
       </c>
       <c r="L11" t="n">
-        <v>1882</v>
+        <v>1983</v>
       </c>
       <c r="M11" t="n">
-        <v>0.926673751328374</v>
+        <v>0.8825012607160867</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8705281090289608</v>
+        <v>0.832438238453276</v>
       </c>
       <c r="O11" t="n">
-        <v>0.825</v>
+        <v>0.7903503733486502</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7906517445687953</v>
+        <v>0.754320987654321</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9129486349582845</v>
+        <v>0.9131175989738241</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9239776276012144</v>
+        <v>0.9135969250119229</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8598906281025464</v>
+        <v>0.8632303014907839</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9079476089854517</v>
+        <v>0.906008766486526</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9080376456215742</v>
+        <v>0.9060746083721165</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1891008174386921</v>
+        <v>0.1749318801089918</v>
       </c>
     </row>
     <row r="12">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1363,49 +1363,49 @@
         <v>14298463</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8277068918260961</v>
+        <v>0.8205067505578394</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.9615128862298711</v>
       </c>
       <c r="J12" t="n">
-        <v>1.002586652871185</v>
+        <v>0.9622348680807036</v>
       </c>
       <c r="K12" t="n">
         <v>1933</v>
       </c>
       <c r="L12" t="n">
-        <v>1938</v>
+        <v>1860</v>
       </c>
       <c r="M12" t="n">
-        <v>0.890608875128999</v>
+        <v>0.9252688172043011</v>
       </c>
       <c r="N12" t="n">
-        <v>0.844799119427628</v>
+        <v>0.8711903392754456</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8060141509433962</v>
+        <v>0.8275648949320148</v>
       </c>
       <c r="P12" t="n">
-        <v>0.773968253968254</v>
+        <v>0.7949231796927188</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9048380282966602</v>
+        <v>0.9144214691239395</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9123717247479102</v>
+        <v>0.9252627032338016</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8615370865360155</v>
+        <v>0.8698865247030811</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9029187064614465</v>
+        <v>0.9150773078887855</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9026301470568164</v>
+        <v>0.9153882599322092</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1830907054871221</v>
+        <v>0.1487738419618529</v>
       </c>
     </row>
     <row r="13">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1443,49 +1443,49 @@
         <v>30288239</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7732478600402537</v>
+        <v>0.813635881873523</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.06414899120538</v>
+        <v>1.021727884117951</v>
       </c>
       <c r="K13" t="n">
         <v>1933</v>
       </c>
       <c r="L13" t="n">
-        <v>2057</v>
+        <v>1975</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8405444822557122</v>
+        <v>0.8886075949367088</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7908057851239669</v>
+        <v>0.8344120819848975</v>
       </c>
       <c r="O13" t="n">
-        <v>0.749862258953168</v>
+        <v>0.7893825735718407</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7172373081463991</v>
+        <v>0.7487593052109182</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9095395176116166</v>
+        <v>0.9189662981810743</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9165910807462426</v>
+        <v>0.9219434685990281</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8646091484056442</v>
+        <v>0.873085601458892</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9071074552366333</v>
+        <v>0.9013867954550479</v>
       </c>
       <c r="U13" t="n">
-        <v>0.906326760541005</v>
+        <v>0.9030441701261431</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2558790593505039</v>
+        <v>0.1841961852861035</v>
       </c>
     </row>
     <row r="14">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1523,49 +1523,49 @@
         <v>42511865</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8357346966327746</v>
+        <v>0.8167132880696127</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9859340704987389</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9860320744956027</v>
+        <v>1.009311950336265</v>
       </c>
       <c r="K14" t="n">
         <v>1933</v>
       </c>
       <c r="L14" t="n">
-        <v>1906</v>
+        <v>1951</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9197271773347324</v>
+        <v>0.8933880061506919</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8649859943977591</v>
+        <v>0.8371584699453551</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8221153846153846</v>
+        <v>0.7905207723815096</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7893713545042126</v>
+        <v>0.7525188916876574</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9167663540945522</v>
+        <v>0.9133540353811062</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9263638668756862</v>
+        <v>0.9165603013867554</v>
       </c>
       <c r="S14" t="n">
-        <v>0.863484805153526</v>
+        <v>0.8557891513404239</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9093739321784589</v>
+        <v>0.9020642234151943</v>
       </c>
       <c r="U14" t="n">
-        <v>0.910222902399491</v>
+        <v>0.9011032930379419</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1494960806270997</v>
+        <v>0.1743869209809264</v>
       </c>
     </row>
     <row r="15">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1603,49 +1603,49 @@
         <v>50995999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7915737107336461</v>
+        <v>0.8173387813259361</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.9706058228183819</v>
       </c>
       <c r="J15" t="n">
-        <v>1.06414899120538</v>
+        <v>0.9710294878427315</v>
       </c>
       <c r="K15" t="n">
         <v>1933</v>
       </c>
       <c r="L15" t="n">
-        <v>2057</v>
+        <v>1877</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8575595527467185</v>
+        <v>0.9104954714970698</v>
       </c>
       <c r="N15" t="n">
-        <v>0.809400826446281</v>
+        <v>0.8593394077448747</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7702479338842976</v>
+        <v>0.8183486238532111</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7343565525383707</v>
+        <v>0.785336856010568</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9155449981420208</v>
+        <v>0.9090940231899541</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9184063189229027</v>
+        <v>0.9160940430889757</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8694066337492048</v>
+        <v>0.8596350510323257</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9065722205607216</v>
+        <v>0.9090703911403852</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9058387601344243</v>
+        <v>0.9085655510780676</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2138857782754759</v>
+        <v>0.1683923705722071</v>
       </c>
     </row>
     <row r="16">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1683,49 +1683,49 @@
         <v>246773155</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8262599807714621</v>
+        <v>0.822410641365379</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.9753874848303937</v>
       </c>
       <c r="J16" t="n">
-        <v>1.020693222969477</v>
+        <v>0.9756854630108639</v>
       </c>
       <c r="K16" t="n">
         <v>1933</v>
       </c>
       <c r="L16" t="n">
-        <v>1973</v>
+        <v>1886</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8915357323872276</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8434125269978402</v>
+        <v>0.861756373937677</v>
       </c>
       <c r="O16" t="n">
-        <v>0.804159445407279</v>
+        <v>0.8193430656934306</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7708074534161491</v>
+        <v>0.7839789888378201</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9178958985340392</v>
+        <v>0.9079660584687866</v>
       </c>
       <c r="R16" t="n">
-        <v>0.918778419093337</v>
+        <v>0.9178620108193565</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8698348655375771</v>
+        <v>0.8639222274053732</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9126657811658768</v>
+        <v>0.9071818502029259</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9132718366507762</v>
+        <v>0.907441685482776</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1612541993281075</v>
+        <v>0.1623978201634877</v>
       </c>
     </row>
     <row r="17">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1756,56 +1756,56 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>14298463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8277068918260961</v>
+        <v>0.5942938372316926</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1.002586652871185</v>
+        <v>1.353336782203828</v>
       </c>
       <c r="K17" t="n">
         <v>1933</v>
       </c>
       <c r="L17" t="n">
-        <v>1938</v>
+        <v>2616</v>
       </c>
       <c r="M17" t="n">
-        <v>0.890608875128999</v>
+        <v>0.6643730886850153</v>
       </c>
       <c r="N17" t="n">
-        <v>0.844799119427628</v>
+        <v>0.6140280561122244</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8060141509433962</v>
+        <v>0.5707666385846673</v>
       </c>
       <c r="P17" t="n">
-        <v>0.773968253968254</v>
+        <v>0.5357301375943186</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9048380282966602</v>
+        <v>0.8978977139369243</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9123717247479102</v>
+        <v>0.9010880653276767</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8615370865360155</v>
+        <v>0.8437806942020702</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9029187064614465</v>
+        <v>0.8898373121625476</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9026301470568164</v>
+        <v>0.8896090773887257</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2212534059945504</v>
+        <v>0.5433242506811989</v>
       </c>
     </row>
     <row r="18">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1836,56 +1836,56 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>30288239</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7732478600402537</v>
+        <v>0.8226538504036932</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1.06414899120538</v>
+        <v>1.023279875840662</v>
       </c>
       <c r="K18" t="n">
         <v>1933</v>
       </c>
       <c r="L18" t="n">
-        <v>2057</v>
+        <v>1978</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8405444822557122</v>
+        <v>0.8923154701718908</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7908057851239669</v>
+        <v>0.8422186322024772</v>
       </c>
       <c r="O18" t="n">
-        <v>0.749862258953168</v>
+        <v>0.7995391705069125</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7172373081463991</v>
+        <v>0.7622291021671826</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9095395176116166</v>
+        <v>0.918325222654212</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9165910807462426</v>
+        <v>0.9215591155100408</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8646091484056442</v>
+        <v>0.8715262141438865</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9071074552366333</v>
+        <v>0.9001054379235679</v>
       </c>
       <c r="U18" t="n">
-        <v>0.906326760541005</v>
+        <v>0.9009531941947535</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2926430517711172</v>
+        <v>0.1831062670299728</v>
       </c>
     </row>
     <row r="19">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1916,56 +1916,56 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>42511865</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8357346966327746</v>
+        <v>0.8363602395989838</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9859340704987389</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9860320744956027</v>
+        <v>1.003103983445422</v>
       </c>
       <c r="K19" t="n">
         <v>1933</v>
       </c>
       <c r="L19" t="n">
-        <v>1906</v>
+        <v>1939</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9197271773347324</v>
+        <v>0.9092315626611656</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8649859943977591</v>
+        <v>0.8547854785478548</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8221153846153846</v>
+        <v>0.8126104890984089</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7893713545042126</v>
+        <v>0.774746192893401</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9167663540945522</v>
+        <v>0.9227118885636272</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9263638668756862</v>
+        <v>0.924534711390032</v>
       </c>
       <c r="S19" t="n">
-        <v>0.863484805153526</v>
+        <v>0.8643463771005508</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9093739321784589</v>
+        <v>0.9062910925112377</v>
       </c>
       <c r="U19" t="n">
-        <v>0.910222902399491</v>
+        <v>0.9049859243594381</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1912806539509537</v>
+        <v>0.1564032697547684</v>
       </c>
     </row>
     <row r="20">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1996,56 +1996,56 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>50995999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7915737107336461</v>
+        <v>0.7318002044978755</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1.06414899120538</v>
+        <v>1.110708742886705</v>
       </c>
       <c r="K20" t="n">
         <v>1933</v>
       </c>
       <c r="L20" t="n">
-        <v>2057</v>
+        <v>2147</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8575595527467185</v>
+        <v>0.8062412668840242</v>
       </c>
       <c r="N20" t="n">
-        <v>0.809400826446281</v>
+        <v>0.7522211253701876</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7702479338842976</v>
+        <v>0.7065616797900263</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7343565525383707</v>
+        <v>0.6692825112107623</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9155449981420208</v>
+        <v>0.9057853969245733</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9184063189229027</v>
+        <v>0.9126319245899206</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8694066337492048</v>
+        <v>0.8540096679516798</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9065722205607216</v>
+        <v>0.9022497688260562</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9058387601344243</v>
+        <v>0.9024093142239475</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2544959128065395</v>
+        <v>0.2964577656675749</v>
       </c>
     </row>
     <row r="21">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2076,56 +2076,56 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>246773155</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8262599807714621</v>
+        <v>0.7282374607987826</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1.020693222969477</v>
+        <v>1.121055354371443</v>
       </c>
       <c r="K21" t="n">
         <v>1933</v>
       </c>
       <c r="L21" t="n">
-        <v>1973</v>
+        <v>2167</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8915357323872276</v>
+        <v>0.8006460544531611</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8434125269978402</v>
+        <v>0.7497556207233627</v>
       </c>
       <c r="O21" t="n">
-        <v>0.804159445407279</v>
+        <v>0.704935064935065</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7708074534161491</v>
+        <v>0.6646341463414634</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.9178958985340392</v>
+        <v>0.9078936865230192</v>
       </c>
       <c r="R21" t="n">
-        <v>0.918778419093337</v>
+        <v>0.9130590610573616</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8698348655375771</v>
+        <v>0.8612045460837121</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9126657811658768</v>
+        <v>0.8955810239519717</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9132718366507762</v>
+        <v>0.8954714354417996</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2021798365122616</v>
+        <v>0.3062670299727521</v>
       </c>
     </row>
     <row r="22">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2160,52 +2160,52 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8273946655381428</v>
+        <v>0.809502617396948</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.9721621796692501</v>
       </c>
       <c r="J22" t="n">
-        <v>1.00054914881933</v>
+        <v>0.9725425590334981</v>
       </c>
       <c r="K22" t="n">
         <v>1821</v>
       </c>
       <c r="L22" t="n">
-        <v>1822</v>
+        <v>1771</v>
       </c>
       <c r="M22" t="n">
-        <v>0.898463227222832</v>
+        <v>0.9079616036137775</v>
       </c>
       <c r="N22" t="n">
-        <v>0.847148736037625</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8056962025316455</v>
+        <v>0.8096795291039895</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7642220699108979</v>
+        <v>0.7663352272727273</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9136807844393261</v>
+        <v>0.9050273969782876</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9254321280038218</v>
+        <v>0.9251468688134656</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8860330713305156</v>
+        <v>0.8781008770019676</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9207452130786663</v>
+        <v>0.9176945895699105</v>
       </c>
       <c r="U22" t="n">
-        <v>0.92158343868508</v>
+        <v>0.9180678715990697</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1633514165159735</v>
+        <v>0.1663747810858144</v>
       </c>
     </row>
     <row r="23">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2240,52 +2240,52 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8375023124875528</v>
+        <v>0.8198555586824715</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9989010990117442</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9989017023613399</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>1821</v>
       </c>
       <c r="L23" t="n">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9048927982407916</v>
+        <v>0.8951125755079626</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8557126030624264</v>
+        <v>0.8405882352941176</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8186429930247305</v>
+        <v>0.7973400886637112</v>
       </c>
       <c r="P23" t="n">
-        <v>0.779532967032967</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9172324245607297</v>
+        <v>0.9067623300643303</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9317291749385743</v>
+        <v>0.9198304136208171</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8882390266242937</v>
+        <v>0.8728515090860738</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9257967190677425</v>
+        <v>0.9134548821217646</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9256694085664811</v>
+        <v>0.914149743121575</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1573236889692586</v>
+        <v>0.1640396964389959</v>
       </c>
     </row>
     <row r="24">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2320,52 +2320,52 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8111437913338786</v>
+        <v>0.794130161204458</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9590980055711315</v>
+        <v>0.9470251327757069</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9599121361889071</v>
+        <v>0.9483800109829764</v>
       </c>
       <c r="K24" t="n">
         <v>1821</v>
       </c>
       <c r="L24" t="n">
-        <v>1748</v>
+        <v>1727</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9193363844393593</v>
+        <v>0.9154603358425014</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8635525507068224</v>
+        <v>0.8580323785803238</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8233731739707836</v>
+        <v>0.8161616161616162</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7826714801444044</v>
+        <v>0.7712609970674487</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9095065985587187</v>
+        <v>0.8982965802258854</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9266625446021762</v>
+        <v>0.9213703552402908</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8841438911533548</v>
+        <v>0.8707885712034353</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9240915732943595</v>
+        <v>0.914629113178915</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9222441694764693</v>
+        <v>0.9143993269945715</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1543098251959011</v>
+        <v>0.1681260945709282</v>
       </c>
     </row>
     <row r="25">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2400,52 +2400,52 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8241821721405483</v>
+        <v>0.8280011948888685</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9950454271712614</v>
+        <v>0.9978009904418118</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9950576606260296</v>
+        <v>0.9978034047226798</v>
       </c>
       <c r="K25" t="n">
         <v>1821</v>
       </c>
       <c r="L25" t="n">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9012141280353201</v>
+        <v>0.9064391854705559</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8462448255470136</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8063694267515924</v>
+        <v>0.8063492063492064</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7653554175293306</v>
+        <v>0.7640990371389271</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9147642453773367</v>
+        <v>0.9185673499380108</v>
       </c>
       <c r="R25" t="n">
-        <v>0.928078782801909</v>
+        <v>0.9316010055165995</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8870644047086884</v>
+        <v>0.8881938906132834</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9243606496337791</v>
+        <v>0.9265197431841563</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9242856305352474</v>
+        <v>0.9262864918352887</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1567209162145871</v>
+        <v>0.1465265615878576</v>
       </c>
     </row>
     <row r="26">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2476,56 +2476,56 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8235902124301044</v>
+        <v>0.8237370121229055</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.9861766109327383</v>
       </c>
       <c r="J26" t="n">
-        <v>1.013179571663921</v>
+        <v>0.9862712795167491</v>
       </c>
       <c r="K26" t="n">
         <v>1821</v>
       </c>
       <c r="L26" t="n">
-        <v>1845</v>
+        <v>1796</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8937669376693766</v>
+        <v>0.905902004454343</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8393271461716937</v>
+        <v>0.8537313432835821</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8022457891453525</v>
+        <v>0.814028314028314</v>
       </c>
       <c r="P26" t="n">
-        <v>0.7645074224021593</v>
+        <v>0.7732030704815074</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9125742022520538</v>
+        <v>0.9092966936993263</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9236601331730445</v>
+        <v>0.9218929094961478</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8764984389424764</v>
+        <v>0.8788298773682748</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9168781825680842</v>
+        <v>0.9181040181095115</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9173343247976952</v>
+        <v>0.9181010498107647</v>
       </c>
       <c r="V26" t="n">
-        <v>0.2101576182136602</v>
+        <v>0.1552831290134267</v>
       </c>
     </row>
     <row r="27">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2546,66 +2546,66 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8273946655381428</v>
+        <v>0.7586145736149561</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1.00054914881933</v>
+        <v>1.064799560680945</v>
       </c>
       <c r="K27" t="n">
         <v>1821</v>
       </c>
       <c r="L27" t="n">
-        <v>1822</v>
+        <v>1939</v>
       </c>
       <c r="M27" t="n">
-        <v>0.898463227222832</v>
+        <v>0.8313563692625064</v>
       </c>
       <c r="N27" t="n">
-        <v>0.847148736037625</v>
+        <v>0.7783278327832783</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8056962025316455</v>
+        <v>0.7360047142015321</v>
       </c>
       <c r="P27" t="n">
-        <v>0.7642220699108979</v>
+        <v>0.6954314720812182</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9136807844393261</v>
+        <v>0.8972748591234807</v>
       </c>
       <c r="R27" t="n">
-        <v>0.9254321280038218</v>
+        <v>0.9174995512374835</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8860330713305156</v>
+        <v>0.8668739264818436</v>
       </c>
       <c r="T27" t="n">
-        <v>0.9207452130786663</v>
+        <v>0.9091577507241659</v>
       </c>
       <c r="U27" t="n">
-        <v>0.92158343868508</v>
+        <v>0.9105935758739073</v>
       </c>
       <c r="V27" t="n">
-        <v>0.208990075890251</v>
+        <v>0.2626970227670753</v>
       </c>
     </row>
     <row r="28">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2626,66 +2626,66 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8375023124875528</v>
+        <v>0.7194994578430193</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9989010990117442</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9989017023613399</v>
+        <v>1.100494233937397</v>
       </c>
       <c r="K28" t="n">
         <v>1821</v>
       </c>
       <c r="L28" t="n">
-        <v>1819</v>
+        <v>2004</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9048927982407916</v>
+        <v>0.7929141716566867</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8557126030624264</v>
+        <v>0.7397769516728625</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8186429930247305</v>
+        <v>0.6980703745743473</v>
       </c>
       <c r="P28" t="n">
-        <v>0.779532967032967</v>
+        <v>0.6544789762340036</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9172324245607297</v>
+        <v>0.8926073943128128</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9317291749385743</v>
+        <v>0.9087918360230131</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8882390266242937</v>
+        <v>0.864317334113214</v>
       </c>
       <c r="T28" t="n">
-        <v>0.9257967190677425</v>
+        <v>0.9044319319251179</v>
       </c>
       <c r="U28" t="n">
-        <v>0.9256694085664811</v>
+        <v>0.9050885905354137</v>
       </c>
       <c r="V28" t="n">
-        <v>0.2019848219497957</v>
+        <v>0.3123175715119673</v>
       </c>
     </row>
     <row r="29">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2706,66 +2706,66 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8111437913338786</v>
+        <v>0.801365676406475</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9590980055711315</v>
+        <v>0.9670697300070306</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9599121361889071</v>
+        <v>0.9676002196595277</v>
       </c>
       <c r="K29" t="n">
         <v>1821</v>
       </c>
       <c r="L29" t="n">
-        <v>1748</v>
+        <v>1762</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9193363844393593</v>
+        <v>0.8995459704880817</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8635525507068224</v>
+        <v>0.8458257160268129</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8233731739707836</v>
+        <v>0.8072368421052631</v>
       </c>
       <c r="P29" t="n">
-        <v>0.7826714801444044</v>
+        <v>0.7676912080057183</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9095065985587187</v>
+        <v>0.89506456099779</v>
       </c>
       <c r="R29" t="n">
-        <v>0.9266625446021762</v>
+        <v>0.9154103599864203</v>
       </c>
       <c r="S29" t="n">
-        <v>0.8841438911533548</v>
+        <v>0.8665859967176415</v>
       </c>
       <c r="T29" t="n">
-        <v>0.9240915732943595</v>
+        <v>0.9093205638714514</v>
       </c>
       <c r="U29" t="n">
-        <v>0.9222441694764693</v>
+        <v>0.9095004144663654</v>
       </c>
       <c r="V29" t="n">
-        <v>0.1961471103327496</v>
+        <v>0.1827203736135435</v>
       </c>
     </row>
     <row r="30">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2786,66 +2786,66 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8241821721405483</v>
+        <v>0.7628479906565736</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9950454271712614</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9950576606260296</v>
+        <v>1.059857221306974</v>
       </c>
       <c r="K30" t="n">
         <v>1821</v>
       </c>
       <c r="L30" t="n">
-        <v>1812</v>
+        <v>1930</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9012141280353201</v>
+        <v>0.8352331606217617</v>
       </c>
       <c r="N30" t="n">
-        <v>0.8462448255470136</v>
+        <v>0.7822001105583195</v>
       </c>
       <c r="O30" t="n">
-        <v>0.8063694267515924</v>
+        <v>0.7411137440758294</v>
       </c>
       <c r="P30" t="n">
-        <v>0.7653554175293306</v>
+        <v>0.6994256541161455</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9147642453773367</v>
+        <v>0.9010026186839606</v>
       </c>
       <c r="R30" t="n">
-        <v>0.928078782801909</v>
+        <v>0.9201597916479988</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8870644047086884</v>
+        <v>0.8753592229673526</v>
       </c>
       <c r="T30" t="n">
-        <v>0.9243606496337791</v>
+        <v>0.9165196692977604</v>
       </c>
       <c r="U30" t="n">
-        <v>0.9242856305352474</v>
+        <v>0.9153010296308211</v>
       </c>
       <c r="V30" t="n">
-        <v>0.2014010507880911</v>
+        <v>0.2545242265032107</v>
       </c>
     </row>
     <row r="31">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2880,52 +2880,52 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8277391694665959</v>
+        <v>0.7521381250532277</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9481809229458519</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9494783086216365</v>
+        <v>1.088412959912136</v>
       </c>
       <c r="K31" t="n">
         <v>1821</v>
       </c>
       <c r="L31" t="n">
-        <v>1729</v>
+        <v>1982</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9375361480624639</v>
+        <v>0.8198789101917255</v>
       </c>
       <c r="N31" t="n">
-        <v>0.8868159203980099</v>
+        <v>0.7705534658785599</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8527236045729657</v>
+        <v>0.7316091954022989</v>
       </c>
       <c r="P31" t="n">
-        <v>0.8191800878477306</v>
+        <v>0.692402717726992</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9122445941580626</v>
+        <v>0.9029246386303933</v>
       </c>
       <c r="R31" t="n">
-        <v>0.9325735419775716</v>
+        <v>0.9146743998268154</v>
       </c>
       <c r="S31" t="n">
-        <v>0.885976327083811</v>
+        <v>0.8726039041623104</v>
       </c>
       <c r="T31" t="n">
-        <v>0.9269929306876199</v>
+        <v>0.911200083722936</v>
       </c>
       <c r="U31" t="n">
-        <v>0.9273807977653444</v>
+        <v>0.910576306558756</v>
       </c>
       <c r="V31" t="n">
-        <v>0.1374321880650995</v>
+        <v>0.2691185055458261</v>
       </c>
     </row>
     <row r="32">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2960,52 +2960,52 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8054510736450647</v>
+        <v>0.789386005393549</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0.9613818892005206</v>
       </c>
       <c r="J32" t="n">
-        <v>1.038989566172433</v>
+        <v>0.9621087314662273</v>
       </c>
       <c r="K32" t="n">
         <v>1821</v>
       </c>
       <c r="L32" t="n">
-        <v>1892</v>
+        <v>1752</v>
       </c>
       <c r="M32" t="n">
-        <v>0.86892177589852</v>
+        <v>0.9058219178082192</v>
       </c>
       <c r="N32" t="n">
-        <v>0.8221343873517787</v>
+        <v>0.841814837522992</v>
       </c>
       <c r="O32" t="n">
-        <v>0.786060606060606</v>
+        <v>0.795364238410596</v>
       </c>
       <c r="P32" t="n">
-        <v>0.7495094833224329</v>
+        <v>0.7494600431965442</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9117758489533213</v>
+        <v>0.9008476515536576</v>
       </c>
       <c r="R32" t="n">
-        <v>0.9236037637645054</v>
+        <v>0.9191322970513317</v>
       </c>
       <c r="S32" t="n">
-        <v>0.8830963820992103</v>
+        <v>0.8697826500334067</v>
       </c>
       <c r="T32" t="n">
-        <v>0.9202738630269842</v>
+        <v>0.9123731774646624</v>
       </c>
       <c r="U32" t="n">
-        <v>0.9208488764267602</v>
+        <v>0.9127366259612918</v>
       </c>
       <c r="V32" t="n">
-        <v>0.2025316455696203</v>
+        <v>0.169877408056042</v>
       </c>
     </row>
     <row r="33">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3040,52 +3040,52 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H33" t="n">
-        <v>0.807061215541047</v>
+        <v>0.8225649808299956</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.9889564905551965</v>
       </c>
       <c r="J33" t="n">
-        <v>1.00384404173531</v>
+        <v>0.9890170236133993</v>
       </c>
       <c r="K33" t="n">
         <v>1821</v>
       </c>
       <c r="L33" t="n">
-        <v>1828</v>
+        <v>1801</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8763676148796499</v>
+        <v>0.8995002776235425</v>
       </c>
       <c r="N33" t="n">
-        <v>0.8236672524897481</v>
+        <v>0.8494047619047619</v>
       </c>
       <c r="O33" t="n">
-        <v>0.78562421185372</v>
+        <v>0.8107761385503528</v>
       </c>
       <c r="P33" t="n">
-        <v>0.7481228668941979</v>
+        <v>0.7726008344923505</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8977439618689302</v>
+        <v>0.9073584114546788</v>
       </c>
       <c r="R33" t="n">
-        <v>0.917090299349829</v>
+        <v>0.9213220262756636</v>
       </c>
       <c r="S33" t="n">
-        <v>0.8699808701179934</v>
+        <v>0.8803271335751423</v>
       </c>
       <c r="T33" t="n">
-        <v>0.9104422231041338</v>
+        <v>0.9162288160149803</v>
       </c>
       <c r="U33" t="n">
-        <v>0.9109869670416524</v>
+        <v>0.9177581853668746</v>
       </c>
       <c r="V33" t="n">
-        <v>0.213381555153707</v>
+        <v>0.166958552247519</v>
       </c>
     </row>
     <row r="34">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3120,52 +3120,52 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H34" t="n">
-        <v>0.822797919308647</v>
+        <v>0.8137622881542911</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9613818892005206</v>
+        <v>0.9800339478767915</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9621087314662273</v>
+        <v>0.9802306425041186</v>
       </c>
       <c r="K34" t="n">
         <v>1821</v>
       </c>
       <c r="L34" t="n">
-        <v>1752</v>
+        <v>1785</v>
       </c>
       <c r="M34" t="n">
-        <v>0.922945205479452</v>
+        <v>0.9064425770308123</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8718577559779277</v>
+        <v>0.8503605769230769</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8350993377483443</v>
+        <v>0.8075178224238496</v>
       </c>
       <c r="P34" t="n">
-        <v>0.7984161267098632</v>
+        <v>0.7637130801687764</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.9122421865076527</v>
+        <v>0.9082022509336107</v>
       </c>
       <c r="R34" t="n">
-        <v>0.927547023298082</v>
+        <v>0.9266468963105563</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8838826660455784</v>
+        <v>0.8791144004255579</v>
       </c>
       <c r="T34" t="n">
-        <v>0.9233730514058418</v>
+        <v>0.9208095374572729</v>
       </c>
       <c r="U34" t="n">
-        <v>0.9222734094102489</v>
+        <v>0.9210830523835887</v>
       </c>
       <c r="V34" t="n">
-        <v>0.1555153707052441</v>
+        <v>0.159369527145359</v>
       </c>
     </row>
     <row r="35">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3200,52 +3200,52 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8333576371556427</v>
+        <v>0.8148809411382499</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.9817129000593525</v>
       </c>
       <c r="J35" t="n">
-        <v>1.014827018121911</v>
+        <v>0.9818780889621087</v>
       </c>
       <c r="K35" t="n">
         <v>1821</v>
       </c>
       <c r="L35" t="n">
-        <v>1848</v>
+        <v>1788</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8971861471861472</v>
+        <v>0.9038031319910514</v>
       </c>
       <c r="N35" t="n">
-        <v>0.85002895193978</v>
+        <v>0.847630473905219</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8138231631382317</v>
+        <v>0.8078913324708926</v>
       </c>
       <c r="P35" t="n">
-        <v>0.7771043771043771</v>
+        <v>0.7670175438596492</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9181156648707716</v>
+        <v>0.9064043825792877</v>
       </c>
       <c r="R35" t="n">
-        <v>0.9281897197562952</v>
+        <v>0.9232991576850468</v>
       </c>
       <c r="S35" t="n">
-        <v>0.8886961410118609</v>
+        <v>0.8787139117455254</v>
       </c>
       <c r="T35" t="n">
-        <v>0.9251291003730622</v>
+        <v>0.9190737552322064</v>
       </c>
       <c r="U35" t="n">
-        <v>0.9249001379040803</v>
+        <v>0.9183770590330542</v>
       </c>
       <c r="V35" t="n">
-        <v>0.1567209162145871</v>
+        <v>0.1628721541155867</v>
       </c>
     </row>
     <row r="36">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3271,61 +3271,61 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8277391694665959</v>
+        <v>0.8147336927252311</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9481809229458519</v>
+        <v>0.9777910397803832</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9494783086216365</v>
+        <v>0.9780340472267984</v>
       </c>
       <c r="K36" t="n">
         <v>1821</v>
       </c>
       <c r="L36" t="n">
-        <v>1729</v>
+        <v>1781</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9375361480624639</v>
+        <v>0.9006176305446378</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8868159203980099</v>
+        <v>0.8487951807228916</v>
       </c>
       <c r="O36" t="n">
-        <v>0.8527236045729657</v>
+        <v>0.8128654970760234</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8191800878477306</v>
+        <v>0.7757404795486601</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9122445941580626</v>
+        <v>0.8970575447417861</v>
       </c>
       <c r="R36" t="n">
-        <v>0.9325735419775716</v>
+        <v>0.9147890063355804</v>
       </c>
       <c r="S36" t="n">
-        <v>0.885976327083811</v>
+        <v>0.8651759938164959</v>
       </c>
       <c r="T36" t="n">
-        <v>0.9269929306876199</v>
+        <v>0.9084340358285273</v>
       </c>
       <c r="U36" t="n">
-        <v>0.9273807977653444</v>
+        <v>0.9090531760444174</v>
       </c>
       <c r="V36" t="n">
-        <v>0.1827203736135435</v>
+        <v>0.1739638061879743</v>
       </c>
     </row>
     <row r="37">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3356,56 +3356,56 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8054510736450647</v>
+        <v>0.7447714754918326</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>1.038989566172433</v>
+        <v>1.053816584294344</v>
       </c>
       <c r="K37" t="n">
         <v>1821</v>
       </c>
       <c r="L37" t="n">
-        <v>1892</v>
+        <v>1919</v>
       </c>
       <c r="M37" t="n">
-        <v>0.86892177589852</v>
+        <v>0.8170922355393434</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8221343873517787</v>
+        <v>0.764182424916574</v>
       </c>
       <c r="O37" t="n">
-        <v>0.786060606060606</v>
+        <v>0.7233154442456768</v>
       </c>
       <c r="P37" t="n">
-        <v>0.7495094833224329</v>
+        <v>0.6812339331619537</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9117758489533213</v>
+        <v>0.885737622343955</v>
       </c>
       <c r="R37" t="n">
-        <v>0.9236037637645054</v>
+        <v>0.9063824968026828</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8830963820992103</v>
+        <v>0.8593978766488288</v>
       </c>
       <c r="T37" t="n">
-        <v>0.9202738630269842</v>
+        <v>0.9002417612005538</v>
       </c>
       <c r="U37" t="n">
-        <v>0.9208488764267602</v>
+        <v>0.9005793562911014</v>
       </c>
       <c r="V37" t="n">
-        <v>0.2475189725627554</v>
+        <v>0.2924693520140105</v>
       </c>
     </row>
     <row r="38">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3436,56 +3436,56 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H38" t="n">
-        <v>0.807061215541047</v>
+        <v>0.8313589528963833</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1.00384404173531</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>1821</v>
       </c>
       <c r="L38" t="n">
-        <v>1828</v>
+        <v>1821</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8763676148796499</v>
+        <v>0.8940142778693025</v>
       </c>
       <c r="N38" t="n">
-        <v>0.8236672524897481</v>
+        <v>0.8476470588235294</v>
       </c>
       <c r="O38" t="n">
-        <v>0.78562421185372</v>
+        <v>0.811906269791007</v>
       </c>
       <c r="P38" t="n">
-        <v>0.7481228668941979</v>
+        <v>0.7764060356652949</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.8977439618689302</v>
+        <v>0.9083588529467841</v>
       </c>
       <c r="R38" t="n">
-        <v>0.917090299349829</v>
+        <v>0.9200273807458733</v>
       </c>
       <c r="S38" t="n">
-        <v>0.8699808701179934</v>
+        <v>0.8792337743869179</v>
       </c>
       <c r="T38" t="n">
-        <v>0.9104422231041338</v>
+        <v>0.9154227392516334</v>
       </c>
       <c r="U38" t="n">
-        <v>0.9109869670416524</v>
+        <v>0.9160070303988429</v>
       </c>
       <c r="V38" t="n">
-        <v>0.2533566841798015</v>
+        <v>0.1716287215411559</v>
       </c>
     </row>
     <row r="39">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3516,56 +3516,56 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H39" t="n">
-        <v>0.822797919308647</v>
+        <v>0.5341588466109694</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9613818892005206</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9621087314662273</v>
+        <v>1.467874794069193</v>
       </c>
       <c r="K39" t="n">
         <v>1821</v>
       </c>
       <c r="L39" t="n">
-        <v>1752</v>
+        <v>2673</v>
       </c>
       <c r="M39" t="n">
-        <v>0.922945205479452</v>
+        <v>0.6026936026936027</v>
       </c>
       <c r="N39" t="n">
-        <v>0.8718577559779277</v>
+        <v>0.5536833855799373</v>
       </c>
       <c r="O39" t="n">
-        <v>0.8350993377483443</v>
+        <v>0.5141916906622789</v>
       </c>
       <c r="P39" t="n">
-        <v>0.7984161267098632</v>
+        <v>0.4744588744588745</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9122421865076527</v>
+        <v>0.8781180003081283</v>
       </c>
       <c r="R39" t="n">
-        <v>0.927547023298082</v>
+        <v>0.8886583679185194</v>
       </c>
       <c r="S39" t="n">
-        <v>0.8838826660455784</v>
+        <v>0.8421055201553439</v>
       </c>
       <c r="T39" t="n">
-        <v>0.9233730514058418</v>
+        <v>0.8832420729009658</v>
       </c>
       <c r="U39" t="n">
-        <v>0.9222734094102489</v>
+        <v>0.8847776535940717</v>
       </c>
       <c r="V39" t="n">
-        <v>0.1973146526561588</v>
+        <v>0.6824284880326912</v>
       </c>
     </row>
     <row r="40">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3596,56 +3596,3336 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8333576371556427</v>
+        <v>0.8175231645364025</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.9481809229458519</v>
       </c>
       <c r="J40" t="n">
-        <v>1.014827018121911</v>
+        <v>0.9494783086216365</v>
       </c>
       <c r="K40" t="n">
         <v>1821</v>
       </c>
       <c r="L40" t="n">
-        <v>1848</v>
+        <v>1729</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8971861471861472</v>
+        <v>0.9242336610757663</v>
       </c>
       <c r="N40" t="n">
-        <v>0.85002895193978</v>
+        <v>0.8756218905472637</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8138231631382317</v>
+        <v>0.8426361802286483</v>
       </c>
       <c r="P40" t="n">
-        <v>0.7771043771043771</v>
+        <v>0.8103953147877013</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9181156648707716</v>
+        <v>0.9018879547275068</v>
       </c>
       <c r="R40" t="n">
-        <v>0.9281897197562952</v>
+        <v>0.9227450742556061</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8886961410118609</v>
+        <v>0.8796452489481461</v>
       </c>
       <c r="T40" t="n">
-        <v>0.9251291003730622</v>
+        <v>0.9192075490997997</v>
       </c>
       <c r="U40" t="n">
-        <v>0.9249001379040803</v>
+        <v>0.9183344865064007</v>
       </c>
       <c r="V40" t="n">
-        <v>0.2031523642732049</v>
+        <v>0.156450671336836</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6739724822482259</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.186161449752883</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2160</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.7430555555555556</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.6924963217263365</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.6532846715328468</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.6138007790762382</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.8867633286527969</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.8979201164517518</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.850376926661478</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.8922878683479185</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.8919796097694592</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.389375364856976</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.8029663161344346</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.040869115364718</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2012</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.8707753479125249</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.822316234796404</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.7802259887005649</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.7440873256519103</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.9159362286114617</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.9128887070042798</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.8662669091401891</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.9010032226474013</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.9007775838045853</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.1931690929451288</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.8323440382554688</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.009311950336265</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1951</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.9082521783700667</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.8524590163934426</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.8069046225863078</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.7682619647355163</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.9285847881080993</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.9306942579439099</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.8790380586011051</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.9140942207492742</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.9147265188813838</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.1534154535274356</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.7856984401228578</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8788959292652573</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.8856699430936368</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1712</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.9608644859813084</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.9113764927718416</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.8369162342475908</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.8996509223003539</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.9255859691913904</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.8763207974938193</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.9207761712748787</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.9203683219968075</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.1466965285554311</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.8398209429878306</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9916883597381694</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.991722710812209</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1917</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.9160146061554513</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.8658129175946548</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.8226865671641791</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.7882882882882883</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.9236942477188667</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.9279632191609668</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.8780397935460575</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.9158932248519205</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.914823016012732</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.14501679731243</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.8212243040616608</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.023797206414899</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1979</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.8913592723597776</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.8423035522066739</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.798503166378814</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.7586633663366337</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.9255374929678948</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.9232738417274633</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.8738530478180729</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.9119478504835098</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.9111385841337527</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.1657334826427772</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.8198123893022407</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.030522503879979</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1992</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.8865461847389559</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.8375200427578835</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.7642725598526704</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.9158197122406689</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.9157833391142365</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.8632427766181194</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.904598115249617</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.9054701225179389</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.1707726763717805</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.7943858857748044</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.068287635799276</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2065</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.8668280871670703</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.8143004115226338</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.7712561711464618</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.7314923619271445</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.9295293620403327</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.9282931185080379</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.8757760847600546</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.9042227345300361</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.9041587981893613</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.2071668533034715</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.7550969997839199</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.108639420589757</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2143</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.8254783014465702</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.7744807121661721</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.7317201472908995</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.6949438202247191</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.9220746506084858</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.9194088066352759</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.8660412051300819</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.9108878575038291</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.9113955401818202</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.2536394176931691</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.8208457981795987</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9479950535164227</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.9493016037247801</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1835</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.9302452316076294</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.882147024504084</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.8430634023854363</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.9056408518386118</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.9214193669061224</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.865408356760887</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.910864255137606</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.9100182822545779</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.1539753639417693</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.7389360980627774</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.131401965856182</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2187</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.8070416095107453</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.7594385285575992</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.7167095115681233</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.6787280701754386</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.9124505004998782</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.9063542571747626</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.8561380100299641</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.8989724740444816</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.8991598746599894</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.2749160134378499</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.827265214142886</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.005173305742369</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1943</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.8975810602161606</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.8435784851811197</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.8030570252792475</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.770253164556962</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.9160501978887292</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.9181487731023685</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.858930823468438</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.9083584122457242</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0.9086345647123868</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.1606942889137738</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.8395881620044378</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.9958527794142726</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.9958613554061045</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1925</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.9106493506493506</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.8614190687361419</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.8205585264408793</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.7848911651728553</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.9237639139847091</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.9309648038313365</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.8818801361362663</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.9186173441141985</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.9199977684530936</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.1550951847704367</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.832173252563925</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9838334710224184</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.9839627521986549</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1902</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.9132492113564669</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.8641212801796744</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.822289156626506</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.7888239116309291</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.9199808601112833</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.9268622244918174</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.8737263597904472</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.9141964808857129</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0.9143875065839516</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.164053751399776</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.8336578198571808</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.9716703377008878</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.9720641489912054</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1879</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.9276210750399149</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.8754266211604096</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.8332315210751374</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.8007915567282322</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.9208167002300187</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.9296173667063712</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.8744512100596062</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.9195514670283687</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.9183123505109336</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.1371780515117581</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.8363666184651901</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.000517330574237</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1934</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.9084798345398138</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.8554881412024269</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8120567375886525</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.7753023551877785</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.9247321192778263</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.9277120173729303</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.8725479637424629</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.9139945175931388</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.9142397831223814</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.1506159014557671</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.7442806553399268</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.106052767718572</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2138</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.8124415341440598</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.7635101636093208</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.7215189873417721</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.6856338028169014</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.8969130002585091</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.9021058732493006</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.8478773384911351</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.8894270065729022</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0.8896618053134093</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.2866741321388578</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.8486558945434285</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.9942931413435602</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9943093636833937</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1922</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.9141519250780437</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.8695169350360911</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.8327380952380953</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.8017960230917255</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.920232265431037</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.9297474749775555</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.8802869697671318</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.917542075471218</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0.9189891637930454</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.1534154535274356</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.7992477035024382</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.048629073978272</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2027</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.8667982239763197</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.8174186778593914</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.7753501400560224</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.7427884615384616</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.917099044005893</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.9220123443391128</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.8672210435667072</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.9128817217074443</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0.913082291105757</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.2054871220604703</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.7838788946569407</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.080703569580962</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2089</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.8535184298707515</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.8023373983739838</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.760693015701137</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.7247972190034763</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.9240778110639767</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.9198959144434162</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.8695785724636333</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.9101349884669913</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.908896262270753</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.8262404442445381</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.012415933781686</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1933</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1957</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.8978027593254982</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.8453159041394336</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.8023323615160349</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.7653701380175659</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.9212206753265859</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.9188651164801368</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.8628804048766821</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.9106292464368865</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.910097464799681</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.1590145576707727</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.8084331728962881</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.985619718640259</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.985722130697419</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1795</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.8896935933147633</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.7990985189954926</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.7590782122905028</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.8960206272331608</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.913386734094461</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.8725655969821351</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.9080359889051284</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0.9084855281681403</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0.1892706449668475</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.8354556786810944</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.994493406023475</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.9945085118066996</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1811</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.9066813914964108</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.857396449704142</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.8202676864244742</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.7810773480662984</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.9175791162023142</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.9302473189122695</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.8935420152092843</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.9273049962207669</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0.9278195571217569</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0.1506931886678722</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.8198473721519965</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.9861766109327383</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.9862712795167491</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1796</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.9047884187082406</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.8495522388059702</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.7676203768318214</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.909107989756097</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.9237064657811117</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.8774229815442888</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.9201063360309591</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0.9192484755601891</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0.160337552742616</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.8389177012570731</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.9867331975516668</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.9868204283360791</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1797</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.9165275459098498</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.8675417661097852</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.8302250803858521</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.791492329149233</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.9194592735481988</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.932468527420607</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.8933986474802346</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.9279644122823889</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0.9275235813256418</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0.1404460518384569</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.8425688926467164</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.994493406023475</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.9945085118066996</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1811</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.9160684704583103</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.8650887573964497</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.8272785213511791</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.7859116022099447</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.9216640637902364</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.9369911962671147</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.8976785924728532</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.9345822201001063</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0.9344600111092454</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0.1338155515370705</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.8221801032661095</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.9811535565217157</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.9813289401427787</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1787</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.910464465584779</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.8541416566626651</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.8148867313915857</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.7780898876404494</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.9054989435837777</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.9263887250681859</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.8787019938130463</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.9182276392346679</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0.9183722841601186</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.1645569620253164</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.8053996505975402</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1.030752333882482</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1877</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.8737346830047948</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.8228929384965832</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.7840978593272171</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.7463672391017173</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.9073794916702568</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.9220096398421656</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.8784966212616556</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.9161221380546525</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0.9161476917855655</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0.2025316455696203</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.8334981577185971</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.00384404173531</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1828</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.9020787746170679</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.8512009373169303</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.8127364438839849</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.7733788395904437</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.9132667974024511</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.9252333125502072</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.8805893820696933</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.921281193095714</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0.9208218195025681</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0.1567209162145871</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.8032063090172216</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1.031850631521142</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1879</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.8738690792974987</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.8208191126279863</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.7819181429444105</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.7420844327176781</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.9106785823848761</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.9195384889370881</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0.8758979856251714</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.9182773258381907</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0.9165149451779269</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0.1916817359855335</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.7990844990678551</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1.050521691378363</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1913</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.8677469942498693</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.8169642857142857</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.7785757031717534</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.7387096774193549</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.9153054682935805</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.9271848687340444</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0.8852702337326284</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0.924049974900773</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0.9231486223651285</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0.2013261000602773</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.8279840630391503</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1.011532125205931</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1842</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.8984799131378935</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.8454386984311447</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.80625</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.7674104124408384</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0.9180517979040702</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.9259658921651701</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.8811796735677894</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0.9205439512046063</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0.9202849653099707</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0.1531042796865582</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.8211808247722827</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.9619520779199763</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.9626578802855574</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1753</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.9201369081574444</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.8688725490196079</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.8325612177365983</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.797841726618705</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.9041279034949073</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.9241890480133929</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.8813229884703728</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0.9180484898381066</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0.918976874023577</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0.1543098251959011</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.8065755580761137</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.9271819687463395</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.9297089511257551</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1693</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.9409332545776727</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.8867684478371501</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.8483804272915231</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.8090225563909774</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.9102723332035294</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.9352339991795714</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0.8908355565153463</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.9296924236251409</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.9292865783885468</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0.1458710066305003</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.8240334517288237</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.9704674895781807</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.970895112575508</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1768</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.919683257918552</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.8676381299332119</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.8283093053735255</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.7864768683274022</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.918275507032993</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.9313965150724658</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.8924689641107934</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0.9295711763132805</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0.9283418945157889</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.1464737793851718</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.8144452778172967</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.9562360996195641</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.957166392092257</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1743</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.9219736087205966</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.8705302096177558</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.8301132578281146</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.7898550724637681</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.9108466722486112</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.9284829223189364</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0.8875201752912972</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.9228056036122143</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.9231727574909</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0.1573236889692586</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.8383399724300163</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.9961485604784754</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.9961559582646897</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1814</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.9090407938257994</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.8588304784406379</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.8199745547073791</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.7835975189524466</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.9184792556405629</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.929718142140237</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0.886024828020442</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.9224131022903136</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0.9226248338687968</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.1537070524412296</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.8085350717979274</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1.00274574409665</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1826</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.8740416210295728</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.8246334310850439</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.7525632262474368</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.8890594923466156</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.9122319525301494</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0.8652301608634506</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0.9049560418608218</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0.9049197746359601</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0.2230259192284509</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.8253806329430634</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.9371496658830201</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.9390444810543658</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1710</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.9456140350877194</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.8967904342353682</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.8610354223433242</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.8240534521158129</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.9178987393468513</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.9413266503289179</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.8988319092478944</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.9351729625783461</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.9353776369896045</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.133212778782399</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.8373309796684801</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.9833890894773064</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.9835255354200988</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1791</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.9229480737018425</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.8706586826347306</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.829567462879277</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.788515406162465</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.923604907934052</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.9351184227976246</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.8933147619215038</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0.9320280666296663</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0.9318726036610423</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.1350210970464135</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.8298256328276012</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.9872894786601247</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.9873695771554091</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1798</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.9093437152391546</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.8580799045915325</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.8187660668380463</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.7811846689895471</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.9112076690012123</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.9258414015419996</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0.8767970808347175</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.9184226343433983</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0.918313964751901</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.1633514165159735</v>
       </c>
     </row>
   </sheetData>
